--- a/Wigan Transfer Note Data Extraction/Assets/IDP Config.xlsx
+++ b/Wigan Transfer Note Data Extraction/Assets/IDP Config.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://defra-my.sharepoint.com/personal/william_skalka_defra_gov_uk/Documents/Documents/GitHub/ea-wigan-waste-transfer-notes/Wigan Transfer Note Data Extraction/Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_F25DC773A252ABDACC1048E8019B74A25BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0F3D82A-5C8A-432A-B22F-8C7ECC00CCBE}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="11_F25DC773A252ABDACC1048E8019B74A25BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D3152B6-0758-4CAB-A713-FF72944D578E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JDickinson" sheetId="1" r:id="rId1"/>
     <sheet name="NCDOwnNotes" sheetId="4" r:id="rId2"/>
     <sheet name="NCDDutyOfCare" sheetId="5" r:id="rId3"/>
-    <sheet name="GlobalMetalRecycling" sheetId="6" r:id="rId4"/>
-    <sheet name="KennysSimplified" sheetId="7" r:id="rId5"/>
-    <sheet name="PriorityPercentages" sheetId="2" r:id="rId6"/>
-    <sheet name="Config" sheetId="3" r:id="rId7"/>
+    <sheet name="KennysSimplified" sheetId="7" r:id="rId4"/>
+    <sheet name="PriorityPercentages" sheetId="2" r:id="rId5"/>
+    <sheet name="Config" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="70">
   <si>
     <t>TaxonomyFieldName</t>
   </si>
@@ -214,21 +213,6 @@
   </si>
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Ref Number</t>
-  </si>
-  <si>
-    <t>Ref Description</t>
-  </si>
-  <si>
-    <t>EWC</t>
-  </si>
-  <si>
-    <t>Material Description</t>
   </si>
   <si>
     <t>Ticket Reference</t>
@@ -317,10 +301,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1204,178 +1184,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FDF949E-B774-44D9-B750-488A9EAA84BC}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057D438A-3465-4587-9337-7C589203F6ED}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1409,7 +1217,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1420,7 +1228,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1431,7 +1239,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1442,7 +1250,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1453,7 +1261,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1464,7 +1272,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1486,7 +1294,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1497,7 +1305,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1508,13 +1316,79 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B83D20-EA89-4187-A3C7-805A43C05B6C}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1523,72 +1397,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B83D20-EA89-4187-A3C7-805A43C05B6C}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1162F53-5482-462B-9855-73DAA292B745}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Wigan Transfer Note Data Extraction/Assets/IDP Config.xlsx
+++ b/Wigan Transfer Note Data Extraction/Assets/IDP Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://defra-my.sharepoint.com/personal/william_skalka_defra_gov_uk/Documents/Documents/GitHub/ea-wigan-waste-transfer-notes/Wigan Transfer Note Data Extraction/Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="11_F25DC773A252ABDACC1048E8019B74A25BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D3152B6-0758-4CAB-A713-FF72944D578E}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="11_F25DC773A252ABDACC1048E8019B74A25BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA3A1A24-7F62-4F16-97AB-40A8F641933F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JDickinson" sheetId="1" r:id="rId1"/>
@@ -185,9 +185,6 @@
     <t>Registration Number (Section C)</t>
   </si>
   <si>
-    <t>Vehicle Registration (Section C)</t>
-  </si>
-  <si>
     <t>D1 Address of Transfer</t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>Receiving Site Authorisation</t>
+  </si>
+  <si>
+    <t>Details (Section C)</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12">
         <v>1</v>
